--- a/output/2026-09-06_15_Slovenia_Primorsko-notranjska_Depolverazione_Trattamento_aria.xlsx
+++ b/output/2026-09-06_15_Slovenia_Primorsko-notranjska_Depolverazione_Trattamento_aria.xlsx
@@ -506,7 +506,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Verificato tramite WebSearch. Azienda reale, attiva dal 1965 come "Elektro delavnica Škrab", oggi Tehnovent David Škrab s.p., guidata da David Škrab. Sede confermata a Vilharjeva cesta 34, 6250 Ilirska Bistrica. Produce e vende ventilatori industriali e componenti per impianti di aspirazione/ventilazione a installatori e aziende B2B: è un produttore/venditore, non un cliente finale del settore. Fonti: tehnovent.si/kontakt, tehnovent.si/o-nas, sloexport.si, mojobrtnik.com, moja-dejavnost.si</t>
+          <t>Verificato tramite WebSearch. Azienda reale, attiva dal 1965 come "Elektro delavnica Škrab", oggi Tehnovent David Škrab s.p., guidata da David Škrab. Sede confermata a Vilharjeva cesta 34, 6250 Ilirska Bistrica. Produce e vende ventilatori industriali e componenti per impianti di aspirazione/ventilazione a installatori e aziende B2B: è un produttore/venditore, non un cliente finale del settore. Fonti: tehnovent.si/kontakt, tehnovent.si/o-nas, sloexport.si, mojobrtnik.com, moja-dejavnost.si [DUPLICATO — vedi anche: 2026-09-06_05_Slovenia_Savinjska_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
